--- a/sources/jack2_step6b.xlsx
+++ b/sources/jack2_step6b.xlsx
@@ -931,6 +931,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
@@ -988,6 +993,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
@@ -1040,6 +1050,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
@@ -1095,6 +1110,11 @@
       <c r="P13" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>052a3efc-5cdf-4aa6-9af6-a58c6ed3b504</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -6029,6 +6049,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
+        </is>
+      </c>
       <c r="R104" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
@@ -6061,6 +6086,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
+        </is>
+      </c>
       <c r="R105" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
@@ -6093,6 +6123,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+        </is>
+      </c>
       <c r="R106" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
@@ -6123,6 +6158,11 @@
       <c r="K107" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">

--- a/sources/jack2_step6b.xlsx
+++ b/sources/jack2_step6b.xlsx
@@ -3184,7 +3184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3375,7 +3375,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4754,7 +4754,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5337,9 +5337,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89">
-        <f>~3+4</f>
-        <v/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -5394,6 +5395,11 @@
       <c r="R89" t="inlineStr">
         <is>
           <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5441,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5483,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5487,6 +5493,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -5539,7 +5550,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5599,6 +5610,11 @@
       <c r="A94" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">

--- a/sources/jack2_step6b.xlsx
+++ b/sources/jack2_step6b.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T107"/>
+  <dimension ref="A1:T112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -2882,6 +2882,11 @@
           <t>b,db,d,DF+1</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>hcf,DF+1</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>Debugger</t>
@@ -2951,20 +2956,10 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wind Up</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Wind Up (1 Rotation)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2988,7 +2983,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gigaton Punch</t>
+          <t>– Gigaton Punch (1 Rotation)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3050,796 +3045,541 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>– DF+1</t>
+          <t>ccw,db,d</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Debugger</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>Wind Up (2 Rotations)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>With b,b+1 input, full 2nd rotation command is b,b+1,b,db,d,df</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>bfcd8070-9fe9-4f68-b19e-bddec360b30a</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>bc7743df-d62c-4baf-90d6-ca367a954aba</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>c03fb65b-aaac-4006-8e2b-0a9f8c08fd8f</t>
+          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>– Gigaton Punch (2 Rotations)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KD +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>mmmm</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
+          <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DF,1,2,1</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2,1</t>
+          <t>ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-6 -8 -2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>+5 +2 +9</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>+5 +2 +9</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15,12,15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
+          <t>Wind Up (3 Rotations)</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>With b,b+1 input, full 3rd rotation command is b,b+1,ccw,b,db,d</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
+          <t>f6c85458-dd91-4d88-91f1-9a557e0c3420</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Windmill</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>– Gigaton Punch (3 Rotations)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10,15,10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
+          <t>e63a69f8-5fec-47ed-a05a-1068334010ce</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>f6c85458-dd91-4d88-91f1-9a557e0c3420</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>– Windmill Backhand</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>+20</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>CF GB</t>
+          <t>Wind Up (4 Rotations)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
+          <t>c0f65cc6-5cf3-4384-bf35-b9b00543eb08</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DF,1,2</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Medium Hammer Rush</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>– Gigaton Punch (4 Rotations)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
+          <t>0b650a95-0538-44cb-a60f-505df7041965</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>c0f65cc6-5cf3-4384-bf35-b9b00543eb08</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-17</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>Wind Up (5 Rotations)</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>27d20b09-dd03-41a8-a3e5-9fb3bbc279ad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>– Gigaton Punch (5 Rotations)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>199</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>199</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
+          <t>e17fd2d9-47bc-4541-8a57-8d670b1585de</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>27d20b09-dd03-41a8-a3e5-9fb3bbc279ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>ccw,ccw,ccw,ccw,ccw,db,d</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>– High Punch</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-17</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>h</t>
+          <t>Wind Up (8 Rotations)</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Completes 8 rotations automatically. No Gigaton Punch follow-up.</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
+          <t>15f7632c-c216-4131-a173-898bf20c3023</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>+2 +12 -1 +1</t>
+          <t>KD +4 +2 +9</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LLmm</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>4f881878-519e-4f9f-bb13-ebe8511b7e9f</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
+          <t>bf72dea8-4c41-4bb6-9420-9305240a53e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>DF,1,2,1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2,1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>Quick Upper Rush</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
+          <t>7507a693-7948-45eb-a05e-3707d923e16d</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>b30faab6-54e4-4123-ab0b-5fb12faa3be2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Windmill</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10,15,10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>1c7f46c4-6ab3-4fdd-90e3-5f642409d3af</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Windmill Backhand</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3847,66 +3587,76 @@
           <t>h</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>CF GB</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
+          <t>82838a4d-d558-42b7-ab73-e05d17ef4b08</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
+          <t>e3e5f6b7-4929-4a52-8c31-e6806f1334ee</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
+          <t>dbb96ec3-9f0f-4e57-b4ca-8de7e5046661</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>DF,1,2</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>Medium Hammer Rush</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -3916,96 +3666,86 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
+          <t>53b77124-e72d-4f20-ae78-8225f04ac648</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jack Hammer</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>32</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>BN GB</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
+          <t>29dfa2dc-0160-4e71-b110-03e973136272</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
+          <t>be700e61-7fed-40b2-a16a-4b062cedd1c9</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SS+1+2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Double Knuckle Swing</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4015,250 +3755,255 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
+          <t>eb9bbfe4-68c3-4e58-baf7-821687138e91</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
+          <t>636b5aa8-46de-464e-81e9-d0bcfa43dc73</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-15 -20</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
+          <t>897a7dd1-1093-48ff-85f1-bebca88601ea</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
+          <t>96ffff19-8555-4463-82fe-458f7c0c053b</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>fb453abc-0836-42af-adee-dc8f713ceae0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-15 -16</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -1 +1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
+          <t>87b157c8-bac6-4b55-a543-03b3e5c1c00f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>acb95787-cedc-4b5b-b8fb-50a3e72d4b5b</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
+          <t>19e50734-0a3e-439a-bb45-d0541eae3da2</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>– 1+2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>– Cross Cut Saw</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4273,7 +4018,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -4283,173 +4028,158 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
+          <t>756e1d64-081b-4d25-aaa0-fa5c3b7a738f</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
+          <t>ecd60ebe-4c07-4ca2-a44b-3748905360dd</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>– ~df+2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>– Megaton Punch</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
+          <t>ac1b3ebe-7028-47a0-be65-5eb121dab8bc</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
+          <t>fe5b804b-6426-463e-b283-4eb22f9998b3</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
+          <t>91a5d27a-8ea9-4505-8341-2bc54479b037</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>JG GB</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
+          <t>06ab7954-5d39-49cc-91e3-02c54893dd53</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
+          <t>a769fb07-8a59-436e-a5fb-3acd34e8e01d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>Jack Hammer</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4464,342 +4194,322 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>BN GB</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
+          <t>41456c1a-f3a2-468f-b0ee-ee2032bb78c8</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
+          <t>de86a0e0-55fd-41e5-a239-a7685c39edbd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DF,2,1,2</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>FC+DF+2,1,2</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Quick Uppercut Rush</t>
+          <t>Double Knuckle Swing</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Juggles on the last hit if the first hit was a counter hit.</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
+          <t>15c368e0-8f76-42a0-bbea-ef3cc510e19c</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
+          <t>2f8a7e04-7a60-430d-bc0a-6a55ed0d3427</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-11 -6 -9 -1</t>
+          <t>-15 -20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>KD +5 +3 +10</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>JG RC</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
+          <t>54667fc1-c443-4001-a9d7-46c1d391bc4d</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
+          <t>36af744c-98c3-48c0-bea9-c96c61093c26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atomic Hook</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-15 -16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
+          <t>14470b5f-e125-4262-857b-20fa6db24ee3</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
+          <t>45985eea-a458-447f-9b9d-941ed088446a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
+          <t>f51b4cde-994c-422f-b3e6-3e932f7d87ff</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DF,2</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>FC+df+2</t>
+          <t>– 1+2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>– Cross Cut Saw</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -4809,54 +4519,59 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>acab70ca-8813-48c6-907e-58ba82b57685</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
+          <t>e7af4cd0-902b-4b89-9c43-ea9365bec42c</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– ~df+2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– Megaton Punch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -4866,54 +4581,59 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
+          <t>773af138-28f0-48ff-9b0e-97e83d2d8d3f</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
+          <t>b671f9fe-a460-4157-8300-00379e99322d</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>fab4def4-7c2d-4882-ac15-2c257a91fc81</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Bravo Knuckle</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4923,225 +4643,245 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG GB</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
+          <t>f79bf7d8-dcd1-4a58-883f-38e113a7b9e1</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>2ecc5ad9-b4ca-485a-884a-0301a91b3509</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>Cross Cut Saw</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
+          <t>23e71f4e-0ab8-4ddc-89c1-4b2fe81234cc</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
+          <t>52606470-ef56-4c68-a311-9fe12c9a5f23</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>DF,2,1,2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FC+DF+2,1,2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>Quick Uppercut Rush</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Juggles on the last hit if the first hit was a counter hit.</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
+          <t>38964142-4e38-457c-9a6d-9ef0fcf12cd4</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
+          <t>8efe400a-6435-45e4-92f5-b9e1d4fd9595</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>f,f+3</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Granite Stomp</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>mmmm</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>JG RC</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
+          <t>f62fd939-223c-47b4-982b-aecff23cfca4</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
+          <t>e85a400e-73a4-495b-917a-82244da3681f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>f+3+4</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>FC+df+3+4</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Giga Shoulder Ram</t>
+          <t>Atomic Hook</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5156,438 +4896,508 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
+          <t>e3ef4e95-cdea-4525-83df-74474e814b2a</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
+          <t>e14fe285-946c-414b-88e4-d7e2f3af2745</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
+          <t>b51b9f18-a0d7-4234-b6c4-e0db8e729094</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+          <t>06e4e99f-b024-4491-a080-43e24bdee8bc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>DF,2</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+          <t>d79c3cf7-3a6f-4c0a-b31a-e35de47e6878</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sit Down</t>
+          <t>– Low Punch</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-7</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>82744639-21bd-464e-acb0-fb430a833b71</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
+          <t>da44dd7b-4cdb-4823-a817-06318a68273c</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>– ~3+4</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>– Hop Hip Press</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>62</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>9cba188e-9985-4f96-83e4-7db5474781d2</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+          <t>51f0fb87-39b1-45cd-ab41-c081312a5d9b</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>– B</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>– Roll Back</t>
+          <t>– High Punch</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-5</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>a96a391b-b0cf-493d-a205-6511f1e34903</t>
+          <t>9dd1c03f-e1e1-4e41-b91a-88df8054ec5c</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>4f15e677-cb84-4d03-b6d8-82c26255c1d9</t>
+          <t>529ea903-bd1d-4081-ab74-eb6b82eaab94</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>0e04bfed-33f9-495b-b9db-252a47602a7d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>– F</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>– Roll Forward</t>
+          <t>Megaton Punch</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-17</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>df8e44d6-d84c-4ee6-8117-15cb0b65ceb6</t>
+          <t>56b1623c-ef98-42a3-be49-2ebc46462a0f</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>0680a704-d8c9-47e5-91a9-98babe1c15af</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>e818b2a1-12e3-409b-8e48-4b059aaa76c0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>– 1,2,1,2</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2,1,2,1</t>
+          <t>f,f+3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>– Sitting Punches</t>
+          <t>Granite Stomp</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-45 -43 -45 -43</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10,10,10,10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>llll</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>1e575213-1523-40b8-9492-0a92235d1799</t>
+          <t>ee6c0589-29fe-439a-8f69-242d8e6811f6</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+          <t>879d1a1f-95b2-4081-aa4b-dc74da0c13c6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
+          <t>f+3+4</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>FC+df+3+4</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spring Hammer - Sit Down</t>
+          <t>Giga Shoulder Ram</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5597,206 +5407,247 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
+          <t>20d7633a-2326-4494-84f9-0a235f1c2fe8</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
+          <t>b0da65f9-bf50-406e-8de8-7db02d0abb2c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>– 1,2,1,2</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2,1,2,1</t>
+          <t>DB+3,4,3,4,3,4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>– Sitting Punches</t>
+          <t>Cossack Kicks</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-45 -43 -45 -43</t>
+          <t>-20 -22 -20 -22...</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-35 -32 -35 -32</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>10,10,10,10</t>
+          <t>18,12,10,12,12,12</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>llll</t>
+          <t>LLLLLL</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
+          <t>674f6841-5fbb-4b15-865f-9ab351c1a0f0</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95"/>
+          <t>4c477a6b-86e6-43f8-911d-93481004b0b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>uf+3+4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Hip Press</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>3be14565-e783-4db3-9168-bf98e290f21d</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>ce4da910-2232-4be6-a896-136d900764e1</t>
+        </is>
+      </c>
+    </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
-        <is>
-          <t>Unblockable Arts</t>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3+4</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Sit Down</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>8ff726df-3bc4-4645-98be-c2fad557ee7d</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="H97" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="I97" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="J97" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="L97" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="M97" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="N97" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="O97" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P97" s="1" t="inlineStr">
-        <is>
-          <t>Taggable</t>
-        </is>
-      </c>
-      <c r="Q97" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="R97" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="S97" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="T97" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>– Hop Hip Press</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>If the Hip Press Misses the opponent, Jack-2 can chain into Sit Down extentions.</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>hcf</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>b,b+1</t>
+          <t>– B</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Gigaton Start Up</t>
+          <t>– Roll Back</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5816,24 +5667,29 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+          <t>a96a391b-b0cf-493d-a205-6511f1e34903</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>67a32d45-116c-42ad-88df-89b38e4ca9aa</t>
+          <t>4f15e677-cb84-4d03-b6d8-82c26255c1d9</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>– b,db,d,df,f,uf,u,ub</t>
+          <t>– F</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>– Wind Up</t>
+          <t>– Roll Forward</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5851,342 +5707,571 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Can be repeated up to 5 times.</t>
-        </is>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
+          <t>df8e44d6-d84c-4ee6-8117-15cb0b65ceb6</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>99aa8796-5bbe-4d4a-8523-9278daf2c772</t>
+          <t>0680a704-d8c9-47e5-91a9-98babe1c15af</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>d1938783-b653-4c21-91d7-5303ce4b61cb</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>–– 1</t>
+          <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>–– Gigaton Punch</t>
+          <t>– Sitting Punches</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-45 -43 -45 -43</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-35 -32 -35 -32</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-35 -32 -35 -32</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
+          <t>10,10,10,10</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>llll</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1e575213-1523-40b8-9492-0a92235d1799</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>71c8d35f-24b6-430d-abc5-2ff4c47a8f3b</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>KND d+1+2</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>0066d9e6-44cc-4c22-b95a-1c01b1cb1dcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>– Sitting Punches</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>10,10,10,10</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Damage increases to 60, 80 and 199 with each extra Wind Up. Becomes Unblockable after 2 Wind Ups.</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>5effdb03-d23f-4671-8daa-b173c35d0ee4</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>8ae507ae-80ca-4f99-8564-71283564636c</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>1f65d946-be2a-4bb4-9a27-18e4ad27b7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="101"/>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>llll</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>eb0c424e-d4b0-438e-bfb7-164bbca1894a</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>01e88eb2-b793-4ba3-9d87-7f7b3ab33381</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>9ea7e1a3-859f-438a-b3fc-0ff0de0e315f</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>Unblockable Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I105" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J105" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K105" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L105" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M105" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N105" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O105" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P105" s="1" t="inlineStr">
+        <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Q105" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="R105" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="S105" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="T105" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="106"/>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
         <is>
           <t>String Hit Arts</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
+      <c r="B108" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="D103" s="1" t="inlineStr">
+      <c r="D108" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="E103" s="1" t="inlineStr">
+      <c r="E108" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="F103" s="1" t="inlineStr">
+      <c r="F108" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
+      <c r="G108" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="H103" s="1" t="inlineStr">
+      <c r="H108" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="I103" s="1" t="inlineStr">
+      <c r="I108" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="J103" s="1" t="inlineStr">
+      <c r="J108" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="K103" s="1" t="inlineStr">
+      <c r="K108" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="L103" s="1" t="inlineStr">
+      <c r="L108" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="M103" s="1" t="inlineStr">
+      <c r="M108" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="N103" s="1" t="inlineStr">
+      <c r="N108" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="O103" s="1" t="inlineStr">
+      <c r="O108" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="P103" s="1" t="inlineStr">
+      <c r="P108" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Q103" s="1" t="inlineStr">
+      <c r="Q108" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="R103" s="1" t="inlineStr">
+      <c r="R108" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="S103" s="1" t="inlineStr">
+      <c r="S108" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="T103" s="1" t="inlineStr">
+      <c r="T108" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>D+2,1,1,1,2,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="R109" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T109" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>D+2,1,1,1,2,1,2,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>10,6,5,7,7,6,6,8,12,35</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>sLLmmmmmlm</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R110" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="T110" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,21,25</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>hmLLLmmmmm</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="R111" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="T111" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr">
+      <c r="Q112" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr">
+      <c r="R112" t="inlineStr">
         <is>
           <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="T112" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
